--- a/branches/fix/promis-29-scoring/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
+++ b/branches/fix/promis-29-scoring/CodeSystem-mii-cs-pro-ssd-12-answers.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T15:11:26+00:00</t>
+    <t>2026-10-14T06:32:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
